--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.59869717510495</v>
+        <v>8.872288290954556</v>
       </c>
       <c r="D2" t="n">
-        <v>47.21611071563508</v>
+        <v>7.6726179912907</v>
       </c>
       <c r="E2" t="n">
-        <v>3.53259121734057</v>
+        <v>0.5740460728178429</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2081387489163156</v>
+        <v>0.03382254669890106</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.53351474042381</v>
+        <v>7.72419614531887</v>
       </c>
       <c r="D3" t="n">
-        <v>47.63238821346771</v>
+        <v>7.740263084688502</v>
       </c>
       <c r="E3" t="n">
-        <v>3.53259121734057</v>
+        <v>0.5740460728178429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2081387489163156</v>
+        <v>0.03382254669890106</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
